--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>111 reqs, 0 modules, 2 tests (ratio 200.0%)</t>
+          <t>206 reqs, 0 modules, 4 tests (ratio 400.0%)</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>342 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>No C/C++ source files found</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>coverage</t>
+          <t>unit-tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -974,11 +974,7 @@
           <t>passed</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>line=0.0%, cond=0.0%</t>
-        </is>
-      </c>
+      <c r="D23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -988,19 +984,15 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>c-coverage</t>
+          <t>unit-tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>No build directory with coverage data found</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1010,15 +1002,59 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>coverage</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>line=0.0%, cond=0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>c-coverage</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>lcov/gcov may not be installed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>c-coverage-gate</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>No C coverage report at .yuleosh/reports/c-coverage.json</t>
         </is>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,19 +500,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>misra-check failed, unit-tests failed, coverage failed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -525,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -715,12 +719,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>No C/C++ source files found</t>
+          <t>4800 business-code violation(s) &gt;= threshold 2000</t>
         </is>
       </c>
     </row>
@@ -953,10 +957,17 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr"/>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>tests/e2e/test_e2e.py: .F
+=================================== FAILURES ===================================
+________________________________ test_crc_real _________________________________
+tests/e2e/test_e2e.py:45: in test_f</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -966,15 +977,19 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>coverage</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>coverage run returned non-zero (1): /Library/Frameworks/Python.framework/Versions/3.13/lib/python3.13/site-packages/coverage/control.py:956: CoverageWarning: No data was collected. (no-data-collected); see https://coverage.readthedocs.i</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -984,15 +999,19 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>c-coverage</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr"/>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>lcov/gcov may not be installed</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1002,59 +1021,15 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>coverage</t>
+          <t>c-coverage-gate</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>line=0.0%, cond=0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>c-coverage</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>lcov/gcov may not be installed</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>c-coverage-gate</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>No C coverage report at .yuleosh/reports/c-coverage.json</t>
         </is>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,23 +500,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>misra-check failed, unit-tests failed, coverage failed</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -529,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -719,12 +715,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>4800 business-code violation(s) &gt;= threshold 2000</t>
+          <t>202 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>
@@ -957,17 +953,10 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>tests/e2e/test_e2e.py: .F
-=================================== FAILURES ===================================
-________________________________ test_crc_real _________________________________
-tests/e2e/test_e2e.py:45: in test_f</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -977,19 +966,15 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>coverage</t>
+          <t>unit-tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>coverage run returned non-zero (1): /Library/Frameworks/Python.framework/Versions/3.13/lib/python3.13/site-packages/coverage/control.py:956: CoverageWarning: No data was collected. (no-data-collected); see https://coverage.readthedocs.i</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -999,19 +984,15 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>c-coverage</t>
+          <t>unit-tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>lcov/gcov may not be installed</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1021,17 +1002,61 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>coverage</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>line=0.0%, cond=0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>c-coverage</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>line=83.33%, branch=0.0%, 2 file(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>c-coverage-gate</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>No C coverage report at .yuleosh/reports/c-coverage.json</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>line_rate=83.3% &gt;= 60%</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,19 +500,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unit-tests failed, coverage failed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -636,7 +640,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>206 reqs, 0 modules, 4 tests (ratio 400.0%)</t>
+          <t>206 reqs, 0 modules, 7 tests (ratio 700.0%)</t>
         </is>
       </c>
     </row>
@@ -720,7 +724,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>202 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>894 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>
@@ -989,10 +993,17 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr"/>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>tests/e2e/test_misra_ci.py: .....F
+=================================== FAILURES ===================================
+_______________________ test_misra_violations_breakdown ________________________
+tests/e2e/test_misra_ci.py:136:</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1007,12 +1018,12 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>line=0.0%, cond=0.0%</t>
+          <t xml:space="preserve">coverage run returned non-zero (1): </t>
         </is>
       </c>
     </row>
@@ -1029,12 +1040,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>line=83.33%, branch=0.0%, 2 file(s)</t>
+          <t>lcov/gcov may not be installed</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1067,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>line_rate=83.3% &gt;= 60%</t>
+          <t>line_rate=96.2% &gt;= 80%</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -507,14 +507,14 @@
         <v>21</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>unit-tests failed, coverage failed</t>
+          <t>plan-lint failed, unit-tests failed, coverage failed</t>
         </is>
       </c>
     </row>
@@ -657,12 +657,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>No task/plan files found</t>
+          <t>/Users/stefan/.openclaw/workspace/yuleASR/tasks/next-phase-plan.md: Missing kind classification; /Users/stefan/.openclaw/workspace/yuleASR/tasks/next-phase-plan.md: Missing T00 three-step sections</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>line_rate=96.2% &gt;= 80%</t>
+          <t>line_rate=37.1% &gt;= 35%</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,23 +500,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>plan-lint failed, unit-tests failed, coverage failed</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -529,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -657,14 +653,10 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>/Users/stefan/.openclaw/workspace/yuleASR/tasks/next-phase-plan.md: Missing kind classification; /Users/stefan/.openclaw/workspace/yuleASR/tasks/next-phase-plan.md: Missing T00 three-step sections</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -724,7 +716,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>894 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>845 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>
@@ -993,17 +985,10 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>tests/e2e/test_misra_ci.py: .....F
-=================================== FAILURES ===================================
-_______________________ test_misra_violations_breakdown ________________________
-tests/e2e/test_misra_ci.py:136:</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1013,19 +998,15 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>coverage</t>
+          <t>unit-tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coverage run returned non-zero (1): </t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1035,19 +1016,15 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>c-coverage</t>
+          <t>unit-tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>lcov/gcov may not be installed</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1057,15 +1034,77 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>coverage</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>line=100.0%, cond=100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>c-coverage</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>lcov/gcov may not be installed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
           <t>c-coverage-gate</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>line_rate=37.1% &gt;= 35%</t>
         </is>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,19 +500,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>coverage failed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -716,7 +720,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>845 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>1127 MISRA violation(s) (372 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1061,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>line=100.0%, cond=100.0%</t>
+          <t>Line coverage 21.62162162162162% &lt; 35.0%</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,23 +500,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>coverage failed</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1061,12 +1057,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Line coverage 21.62162162162162% &lt; 35.0%</t>
+          <t>line=21.62162162162162%, cond=21.62162162162162%</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,19 +500,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>plan-lint failed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -653,10 +657,14 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>/Users/stefan/.openclaw/workspace/yuleASR/tasks/v130-to-v140-plan.md: Missing kind classification; /Users/stefan/.openclaw/workspace/yuleASR/tasks/v130-to-v140-plan.md: Missing T00 three-step sections</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -711,12 +719,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1127 MISRA violation(s) (372 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>1141 MISRA violation(s) (372 required, 4 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,23 +500,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>plan-lint failed</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -529,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -657,14 +653,10 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>/Users/stefan/.openclaw/workspace/yuleASR/tasks/v130-to-v140-plan.md: Missing kind classification; /Users/stefan/.openclaw/workspace/yuleASR/tasks/v130-to-v140-plan.md: Missing T00 three-step sections</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -724,7 +716,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1141 MISRA violation(s) (372 required, 4 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>1134 MISRA violation(s) (366 required, 4 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1074,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>c-coverage</t>
+          <t>coverage-regression</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>lcov/gcov may not be installed</t>
+          <t>No regression detected</t>
         </is>
       </c>
     </row>
@@ -1104,15 +1096,37 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
+          <t>c-coverage</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>lcov/gcov may not be installed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>c-coverage-gate</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>line_rate=37.1% &gt;= 35%</t>
         </is>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,19 +500,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unit-tests failed, coverage failed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -716,7 +720,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1134 MISRA violation(s) (366 required, 4 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>768 MISRA violation(s) (0 required, 4 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>
@@ -1039,10 +1043,17 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr"/>
+          <t>failed</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>tests/test_manifest.py: ....F
+=================================== FAILURES ===================================
+__________________ TestManifest.test_traceability_established __________________
+tests/test_manifest.py:55: in te</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1057,12 +1068,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>line=21.62162162162162%, cond=21.62162162162162%</t>
+          <t xml:space="preserve">coverage run returned non-zero (1): </t>
         </is>
       </c>
     </row>
@@ -1123,12 +1134,12 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>line_rate=37.1% &gt;= 35%</t>
+          <t>No C coverage report at .yuleosh/reports/c-coverage.json</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,23 +500,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>failed</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>unit-tests failed, coverage failed</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -529,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -568,7 +564,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>yaml-validation</t>
+          <t>methodology-grilling-alignment</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -576,7 +572,11 @@
           <t>passed</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr"/>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>spec.md 无决策记录 — 存量项目降级（无 .osh/specs/ 活跃流程，建议后续新 spec 补充 Grilling 记录，不阻断）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>spec-validation</t>
+          <t>methodology-domain-model</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0 missing, 3 req keywords found</t>
+          <t>CONTEXT.md 存在且为纯术语表</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>architecture-review</t>
+          <t>methodology-two-axis-review</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 modules: </t>
+          <t>最近报告 yuleasr-compliance-fix.md 缺双轴之一（应含 Standards + Spec 两节）</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>requirements-trace</t>
+          <t>methodology-tight-loop-debug</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>206 reqs, 0 modules, 7 tests (ratio 700.0%)</t>
+          <t>yuleasr-compliance-fix.md 无复现回路证据（应含复现步骤/回路描述）</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>plan-lint</t>
+          <t>methodology-vertical-slices</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -660,7 +660,11 @@
           <t>passed</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>无 plan 文件（跳过，软检查）</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -670,17 +674,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>docsync-gate</t>
+          <t>methodology-handoff</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Sync gate: warning | 3 total, 0 error(s), 0 warning(s)</t>
+          <t>无交接文档（跳过，软检查）</t>
         </is>
       </c>
     </row>
@@ -692,7 +696,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>clang-tidy</t>
+          <t>methodology-gate</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -700,7 +704,11 @@
           <t>passed</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>4 pass, 2 soft, 0 hard</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -710,19 +718,15 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>misra-check</t>
+          <t>yaml-validation</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>768 MISRA violation(s) (0 required, 4 advisory) — see .yuleosh/reports/misra-report.json</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -732,7 +736,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>spec-validation</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -740,7 +744,11 @@
           <t>passed</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>0 missing, 3 req keywords found</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -750,7 +758,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>architecture-review</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -758,7 +766,11 @@
           <t>passed</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 modules: </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -768,7 +780,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>requirements-trace</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -776,7 +788,11 @@
           <t>passed</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>249 reqs, 0 modules, 7 tests (ratio 700.0%)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -786,7 +802,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>plan-lint</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -804,15 +820,19 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>docsync-gate</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sync gate: warning | 3 total, 0 error(s), 0 warning(s)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -822,7 +842,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>clang-tidy</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -840,15 +860,19 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>misra-check</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>36219 MISRA violation(s) (14498 required, 20530 advisory) — see .yuleosh/reports/misra-report.json</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1043,17 +1067,10 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>tests/test_manifest.py: ....F
-=================================== FAILURES ===================================
-__________________ TestManifest.test_traceability_established __________________
-tests/test_manifest.py:55: in te</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1063,19 +1080,15 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>coverage</t>
+          <t>unit-tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>failed</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coverage run returned non-zero (1): </t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1085,7 +1098,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>coverage-regression</t>
+          <t>unit-tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1093,11 +1106,7 @@
           <t>passed</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>No regression detected</t>
-        </is>
-      </c>
+      <c r="D29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1107,19 +1116,15 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>c-coverage</t>
+          <t>unit-tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>lcov/gcov may not be installed</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1129,17 +1134,515 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/framework/scripts/test_config_script.py: no tests collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/framework/scripts/test_psa_constant_names.py: no tests collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/framework/scripts/test_psa_compliance.py: no tests collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/framework/scripts/mbedtls_framework/test_driver.py: no tests collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/framework/scripts/mbedtls_framework/test_case.py: no tests collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/framework/scripts/mbedtls_framework/test_data_generation.py: no tests collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/tests/scripts/test_config_script.py: no tests collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/tests/scripts/test_psa_constant_names.py: no tests collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/tests/scripts/test_psa_compliance.py: no tests collected</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>unit-tests</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>coverage</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>line=21.62162162162162%, cond=21.62162162162162%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>coverage-regression</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>No regression detected</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>c-coverage</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>line=75.84%, branch=0.0%, 7 file(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
           <t>c-coverage-gate</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>No C coverage report at .yuleosh/reports/c-coverage.json</t>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>line_rate=75.8% &gt;= 35%</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>最近报告 yuleasr-compliance-fix.md 缺双轴之一（应含 Standards + Spec 两节）</t>
+          <t>最近报告 yuleasr-ci-fix-20260807.md 缺双轴之一（应含 Standards + Spec 两节）</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>yuleasr-compliance-fix.md 无复现回路证据（应含复现步骤/回路描述）</t>
+          <t>yuleasr-ci-fix-20260807.md 无复现回路证据（应含复现步骤/回路描述）</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>36219 MISRA violation(s) (14498 required, 20530 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>31433 MISRA violation(s) (11005 required, 19285 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>31433 MISRA violation(s) (11005 required, 19285 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>28103 MISRA violation(s) (8378 required, 18592 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>28103 MISRA violation(s) (8378 required, 18592 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>27541 MISRA violation(s) (744 required, 13048 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>27541 MISRA violation(s) (744 required, 13048 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>26699 MISRA violation(s) (219 required, 13047 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>26699 MISRA violation(s) (219 required, 13047 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>2530 MISRA violation(s) (30 required, 29 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>

--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -500,19 +500,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>clang-tidy failed, coverage failed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -525,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -574,7 +578,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>spec.md 无决策记录 — 存量项目降级（无 .osh/specs/ 活跃流程，建议后续新 spec 补充 Grilling 记录，不阻断）</t>
+          <t>2025-04-23-education-community-phase.md 无决策记录 — 存量项目降级（无 .osh/specs/ 活跃流程，建议后续新 spec 补充 Grilling 记录，不阻断）</t>
         </is>
       </c>
     </row>
@@ -618,7 +622,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>最近报告 yuleasr-ci-fix-20260807.md 缺双轴之一（应含 Standards + Spec 两节）</t>
+          <t>无评审报告（reports/*.md）可检查双轴</t>
         </is>
       </c>
     </row>
@@ -635,12 +639,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>yuleasr-ci-fix-20260807.md 无复现回路证据（应含复现步骤/回路描述）</t>
+          <t>无调试/修复报告（跳过，软检查）</t>
         </is>
       </c>
     </row>
@@ -706,7 +710,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>4 pass, 2 soft, 0 hard</t>
+          <t>5 pass, 1 soft, 0 hard</t>
         </is>
       </c>
     </row>
@@ -741,12 +745,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0 missing, 3 req keywords found</t>
+          <t>MISRA acceptance matrix (specs/misra-acceptance-matrix.md)</t>
         </is>
       </c>
     </row>
@@ -790,7 +794,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>249 reqs, 0 modules, 7 tests (ratio 700.0%)</t>
+          <t>154 reqs, 0 modules, 7 tests (ratio 700.0%)</t>
         </is>
       </c>
     </row>
@@ -807,10 +811,14 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>No task/plan files found</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -825,12 +833,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Sync gate: warning | 3 total, 0 error(s), 0 warning(s)</t>
+          <t>Sync gate: passed | 3 total, 0 error(s), 0 warning(s)</t>
         </is>
       </c>
     </row>
@@ -847,10 +855,14 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>clang-tidy not installed</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -865,12 +877,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>2530 MISRA violation(s) (30 required, 29 advisory) — see .yuleosh/reports/misra-report.json</t>
+          <t>74 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>
@@ -1283,10 +1295,14 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr"/>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/framework/scripts/test_config_script.py: no tests collected</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1319,10 +1335,14 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr"/>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/framework/scripts/test_psa_constant_names.py: no tests collected</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1342,7 +1362,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>third_party/mbedtls/framework/scripts/test_config_script.py: no tests collected</t>
+          <t>third_party/mbedtls/framework/scripts/test_psa_compliance.py: no tests collected</t>
         </is>
       </c>
     </row>
@@ -1359,10 +1379,14 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>third_party/mbedtls/framework/scripts/mbedtls_framework/test_driver.py: no tests collected</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1382,7 +1406,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>third_party/mbedtls/framework/scripts/test_psa_constant_names.py: no tests collected</t>
+          <t>third_party/mbedtls/framework/scripts/mbedtls_framework/test_case.py: no tests collected</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1428,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>third_party/mbedtls/framework/scripts/test_psa_compliance.py: no tests collected</t>
+          <t>third_party/mbedtls/framework/scripts/mbedtls_framework/test_data_generation.py: no tests collected</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1450,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>third_party/mbedtls/framework/scripts/mbedtls_framework/test_driver.py: no tests collected</t>
+          <t>third_party/mbedtls/tests/scripts/test_config_script.py: no tests collected</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1472,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>third_party/mbedtls/framework/scripts/mbedtls_framework/test_case.py: no tests collected</t>
+          <t>third_party/mbedtls/tests/scripts/test_psa_constant_names.py: no tests collected</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1494,7 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>third_party/mbedtls/framework/scripts/mbedtls_framework/test_data_generation.py: no tests collected</t>
+          <t>third_party/mbedtls/tests/scripts/test_psa_compliance.py: no tests collected</t>
         </is>
       </c>
     </row>
@@ -1487,14 +1511,10 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>third_party/mbedtls/tests/scripts/test_config_script.py: no tests collected</t>
-        </is>
-      </c>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -1504,17 +1524,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>coverage</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>failed</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>third_party/mbedtls/tests/scripts/test_psa_constant_names.py: no tests collected</t>
+          <t>Line coverage 0.0% &lt; 40.0%</t>
         </is>
       </c>
     </row>
@@ -1526,17 +1546,17 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>coverage-regression</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>skipped</t>
+          <t>passed</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>third_party/mbedtls/tests/scripts/test_psa_compliance.py: no tests collected</t>
+          <t>No regression detected</t>
         </is>
       </c>
     </row>
@@ -1548,15 +1568,19 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>unit-tests</t>
+          <t>c-coverage</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr"/>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>No build directory with coverage data found</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1566,7 +1590,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>coverage</t>
+          <t>c-coverage-gate</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -1576,73 +1600,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>line=21.62162162162162%, cond=21.62162162162162%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>coverage-regression</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>No regression detected</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>c-coverage</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>line=75.84%, branch=0.0%, 7 file(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>c-coverage-gate</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>line_rate=75.8% &gt;= 35%</t>
+          <t>line_rate=91.6% &gt;= 40%</t>
         </is>
       </c>
     </row>
